--- a/data/trans_orig/P36B02_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36B02_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>646679</t>
+          <t>647027</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>669080</t>
+          <t>669480</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>644362</t>
+          <t>645766</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>666177</t>
+          <t>667048</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1298373</t>
+          <t>1298759</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1330471</t>
+          <t>1330005</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24932</t>
+          <t>24532</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47333</t>
+          <t>46985</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22174</t>
+          <t>21303</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43989</t>
+          <t>42585</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51892</t>
+          <t>52358</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>83990</t>
+          <t>83604</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>867181</t>
+          <t>865775</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>901955</t>
+          <t>901842</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>886399</t>
+          <t>885738</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>917596</t>
+          <t>918360</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1762637</t>
+          <t>1763087</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1809281</t>
+          <t>1811873</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,87%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>59845</t>
+          <t>59958</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>94619</t>
+          <t>96025</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50797</t>
+          <t>50033</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>81994</t>
+          <t>82655</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>120912</t>
+          <t>118320</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>167556</t>
+          <t>167106</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>612288</t>
+          <t>612996</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>641008</t>
+          <t>640872</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>627742</t>
+          <t>627793</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>651862</t>
+          <t>651022</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1247667</t>
+          <t>1249626</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1286792</t>
+          <t>1285007</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,4%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37501</t>
+          <t>37637</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66221</t>
+          <t>65513</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30847</t>
+          <t>31687</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54967</t>
+          <t>54916</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>74426</t>
+          <t>76211</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>113551</t>
+          <t>111592</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>851933</t>
+          <t>853751</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>885600</t>
+          <t>885017</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>969411</t>
+          <t>968938</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>997967</t>
+          <t>997682</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1834030</t>
+          <t>1834302</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1875982</t>
+          <t>1878128</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,86%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>55740</t>
+          <t>56323</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>89407</t>
+          <t>87589</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>40645</t>
+          <t>40930</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>69201</t>
+          <t>69674</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>103970</t>
+          <t>101824</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>145922</t>
+          <t>145650</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3010865</t>
+          <t>3011724</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3070960</t>
+          <t>3071974</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3157344</t>
+          <t>3159450</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3209454</t>
+          <t>3214503</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6182195</t>
+          <t>6188622</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6267216</t>
+          <t>6266671</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,18%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>204701</t>
+          <t>203687</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>264796</t>
+          <t>263937</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>168611</t>
+          <t>163562</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>220721</t>
+          <t>218615</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>386510</t>
+          <t>387055</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>471531</t>
+          <t>465104</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>654416</t>
+          <t>655314</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>680223</t>
+          <t>678897</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>654042</t>
+          <t>653742</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>676330</t>
+          <t>676429</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1317278</t>
+          <t>1315966</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1349962</t>
+          <t>1350151</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,4%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23246</t>
+          <t>24572</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49053</t>
+          <t>48155</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20720</t>
+          <t>20621</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43008</t>
+          <t>43308</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>50557</t>
+          <t>50368</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>83241</t>
+          <t>84553</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>945450</t>
+          <t>947451</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>978207</t>
+          <t>978181</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>959216</t>
+          <t>959811</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>989970</t>
+          <t>989321</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1917023</t>
+          <t>1917179</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1959671</t>
+          <t>1960397</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,67%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>39740</t>
+          <t>39766</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>72497</t>
+          <t>70496</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>41236</t>
+          <t>41885</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>71990</t>
+          <t>71395</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>89482</t>
+          <t>88756</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>132130</t>
+          <t>131974</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>659674</t>
+          <t>660717</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>696243</t>
+          <t>695219</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>702914</t>
+          <t>700910</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>732977</t>
+          <t>731125</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1374060</t>
+          <t>1374184</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1420271</t>
+          <t>1420961</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,77%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61380</t>
+          <t>62404</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>97949</t>
+          <t>96906</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41179</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>71242</t>
+          <t>73246</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>111508</t>
+          <t>110818</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>157719</t>
+          <t>157595</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>868484</t>
+          <t>868038</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>900059</t>
+          <t>899624</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>968090</t>
+          <t>964899</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>998634</t>
+          <t>997979</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1844599</t>
+          <t>1844891</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1890801</t>
+          <t>1890590</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,68%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46767</t>
+          <t>47202</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>78342</t>
+          <t>78788</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51340</t>
+          <t>51995</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>81884</t>
+          <t>85075</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>105998</t>
+          <t>106209</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>152200</t>
+          <t>151908</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3161665</t>
+          <t>3165996</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3227948</t>
+          <t>3224637</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3313344</t>
+          <t>3314081</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3374125</t>
+          <t>3372541</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6498776</t>
+          <t>6501487</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6586109</t>
+          <t>6583665</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,35%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>197917</t>
+          <t>201228</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>264200</t>
+          <t>259869</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>178260</t>
+          <t>179844</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>239041</t>
+          <t>238304</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>392141</t>
+          <t>394585</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>479474</t>
+          <t>476763</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>609275</t>
+          <t>609526</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>637593</t>
+          <t>637816</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>629028</t>
+          <t>629620</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>650538</t>
+          <t>649750</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1247298</t>
+          <t>1245981</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1282180</t>
+          <t>1282473</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,36%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36315</t>
+          <t>36092</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>64382</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20446</t>
+          <t>21234</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41956</t>
+          <t>41364</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>62712</t>
+          <t>62419</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>97594</t>
+          <t>98911</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>915115</t>
+          <t>915359</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>952413</t>
+          <t>953237</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>951630</t>
+          <t>954362</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>986224</t>
+          <t>986146</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1878739</t>
+          <t>1880796</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1928456</t>
+          <t>1930240</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,5%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>69049</t>
+          <t>68225</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>106347</t>
+          <t>106103</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>56689</t>
+          <t>56767</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>91283</t>
+          <t>88551</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>135919</t>
+          <t>134135</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>185636</t>
+          <t>183579</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>652543</t>
+          <t>651733</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>687851</t>
+          <t>687961</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>718251</t>
+          <t>718398</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>746125</t>
+          <t>745653</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1380997</t>
+          <t>1380369</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1427791</t>
+          <t>1426164</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,46%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69558</t>
+          <t>69448</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>104866</t>
+          <t>105676</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38886</t>
+          <t>39358</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>66760</t>
+          <t>66613</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>114629</t>
+          <t>116256</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>161423</t>
+          <t>162051</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,51%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>860522</t>
+          <t>863033</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>890450</t>
+          <t>890743</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>968559</t>
+          <t>969095</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>997820</t>
+          <t>998169</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1841414</t>
+          <t>1838209</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1883372</t>
+          <t>1882895</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,22%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44220</t>
+          <t>43927</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>74148</t>
+          <t>71637</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>44847</t>
+          <t>44498</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74108</t>
+          <t>73572</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>93965</t>
+          <t>94442</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>135923</t>
+          <t>139128</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3074831</t>
+          <t>3074343</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3142986</t>
+          <t>3139692</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3301378</t>
+          <t>3301831</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3359736</t>
+          <t>3356938</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6397489</t>
+          <t>6394732</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6478012</t>
+          <t>6479156</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,51%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>244462</t>
+          <t>247756</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>312617</t>
+          <t>313105</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>181839</t>
+          <t>184637</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>240197</t>
+          <t>239744</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>451011</t>
+          <t>449867</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>531534</t>
+          <t>534291</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>559908</t>
+          <t>609046</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>539841</t>
+          <t>586640</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>576334</t>
+          <t>625476</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>612217</t>
+          <t>662384</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>597528</t>
+          <t>648066</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>623682</t>
+          <t>675790</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1172125</t>
+          <t>1271429</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1146050</t>
+          <t>1245288</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1193155</t>
+          <t>1294108</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,91%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>75533</t>
+          <t>81664</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59107</t>
+          <t>65234</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>95600</t>
+          <t>104070</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>63153</t>
+          <t>70338</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51688</t>
+          <t>56932</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77842</t>
+          <t>84656</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>138686</t>
+          <t>152002</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>117656</t>
+          <t>129323</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>164761</t>
+          <t>178143</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1099339</t>
+          <t>943395</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1066751</t>
+          <t>917439</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1150667</t>
+          <t>963230</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>875668</t>
+          <t>976620</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>859740</t>
+          <t>958074</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>890056</t>
+          <t>993978</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1975009</t>
+          <t>1920015</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1940538</t>
+          <t>1889869</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2035885</t>
+          <t>1945358</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>91,77%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>93525</t>
+          <t>105522</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42197</t>
+          <t>85687</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>126113</t>
+          <t>131478</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>82438</t>
+          <t>94218</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>68050</t>
+          <t>76860</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>98366</t>
+          <t>112764</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>175962</t>
+          <t>199740</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>115086</t>
+          <t>174397</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>210433</t>
+          <t>229886</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>567105</t>
+          <t>653413</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>541605</t>
+          <t>626866</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>589385</t>
+          <t>677519</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>827709</t>
+          <t>691819</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>789380</t>
+          <t>673096</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>880842</t>
+          <t>708916</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1394814</t>
+          <t>1345231</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1347492</t>
+          <t>1309960</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1478153</t>
+          <t>1375092</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>85,13%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>137575</t>
+          <t>149660</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>115295</t>
+          <t>125554</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>163075</t>
+          <t>176207</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>105657</t>
+          <t>120440</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52524</t>
+          <t>103343</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>143986</t>
+          <t>139163</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>243232</t>
+          <t>270101</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>159893</t>
+          <t>240240</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>290554</t>
+          <t>305372</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,9%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>821120</t>
+          <t>873682</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>795524</t>
+          <t>848709</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>841667</t>
+          <t>896523</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>913091</t>
+          <t>991860</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>740764</t>
+          <t>970598</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>980732</t>
+          <t>1008681</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1734211</t>
+          <t>1865543</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1518465</t>
+          <t>1835959</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1803922</t>
+          <t>1892529</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,73%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>105711</t>
+          <t>116380</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>85164</t>
+          <t>93539</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>131307</t>
+          <t>141353</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>181841</t>
+          <t>127181</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>114200</t>
+          <t>110360</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>354168</t>
+          <t>148443</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>287552</t>
+          <t>243561</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>217841</t>
+          <t>216575</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>503298</t>
+          <t>273145</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3047473</t>
+          <t>3079536</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2989897</t>
+          <t>3032838</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3136156</t>
+          <t>3124665</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3228685</t>
+          <t>3322683</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3024967</t>
+          <t>3286012</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3314975</t>
+          <t>3355599</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>6276158</t>
+          <t>6402219</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6055024</t>
+          <t>6349366</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6388820</t>
+          <t>6455660</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>88,83%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>412344</t>
+          <t>453226</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>323661</t>
+          <t>408097</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>469920</t>
+          <t>499924</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>433089</t>
+          <t>412177</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>346799</t>
+          <t>379261</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>636807</t>
+          <t>448848</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>845433</t>
+          <t>865403</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>732771</t>
+          <t>811962</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1066567</t>
+          <t>918256</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>12,63%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3661774</t>
+          <t>3734860</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3661774</t>
+          <t>3734860</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3661774</t>
+          <t>3734860</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7121591</t>
+          <t>7267622</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7121591</t>
+          <t>7267622</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7121591</t>
+          <t>7267622</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
